--- a/fundraiser_forms/013_gala_dinner_fundraising_event_feedback_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/013_gala_dinner_fundraising_event_feedback_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -968,8 +968,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -997,12 +997,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'donor'}</t>
+          <t>donor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Donor'}</t>
+          <t>Donor</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'attendee'}</t>
+          <t>attendee</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Attendee'}</t>
+          <t>Attendee</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment'}</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment'}</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'dancing'}</t>
+          <t>dancing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Dancing'}</t>
+          <t>Dancing</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
